--- a/research/PMP_ITES_Companies_USA.xlsx
+++ b/research/PMP_ITES_Companies_USA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,12 +471,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>https://www.accenture.com</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1467373/000146737325000217/acn-20250831.htm</t>
         </is>
@@ -503,7 +503,7 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>https://www2.deloitte.com</t>
         </is>
@@ -530,12 +530,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>https://www.ibm.com/services</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/51143/000005114326000010/ibm-20251231.htm</t>
         </is>
@@ -554,7 +554,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ernst &amp; Young (EY)</t>
+          <t>PricewaterhouseCoopers (PwC)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -562,26 +562,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>https://www.ey.com</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.pwc.com</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FY2023 EY Value Realized report: record $385 million invested in training, delivering an all-time-high 24 million training hours, averaging 61 hours per employee | EY measures training ROI via average spend-per-employee | 2025 EY research found employees with 80+ hours of annual AI training reported productivity gains averaging 14 hours/week, well above the 8-hour median</t>
+          <t>Over 315,000 PwC people have taken part in AI upskilling since July 2023, much of it through the network's AI Academy | PwC invested US$3.1 billion network-wide including acquisitions/investments to expand professional capability in AI, tech, consulting, business strategy and tax | Nearly US$1.5 billion invested to scale AI capabilities, including AI hubs and Centres of Excellence used for internal upskilling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EY Value Realized / Global Review reports and EY 2025 AI training research</t>
+          <t>PwC Global Annual Review 2025</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -589,26 +589,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>https://www.kpmg.com</t>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=CAP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KPMG Lakehouse (Lake Nona, FL) delivers over 1 million hours of in-person professional development annually for US-based employees and partners | In 2024, 80,000+ KPMG global employees took part in '24 Hours of AI' and 'Summer of AI' training programs | Rolled out 57,000+ Microsoft Copilot licenses firmwide to support AI-era skill building</t>
+          <t>Average of 97.2 learning hours per employee in FY2025, including learning in the flow of work | ESG policy target: grow average learning hours per employee by 5% every year for lifelong learning | Learning &amp; Development careers page highlights structured upskilling paths as part of employee value proposition</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KPMG Global press releases, KPMG Lakehouse program materials</t>
+          <t>Capgemini 2025 Universal Registration Document</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers (PwC)</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -616,26 +621,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>https://www.pwc.com</t>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.infosys.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=INFY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Over 315,000 PwC people have taken part in AI upskilling since July 2023, much of it through the network's AI Academy | PwC invested US$3.1 billion network-wide including acquisitions/investments to expand professional capability in AI, tech, consulting, business strategy and tax | Nearly US$1.5 billion invested to scale AI capabilities, including AI hubs and Centres of Excellence used for internal upskilling</t>
+          <t>FY2024-25 annual average training hours per employee reported at 71.35 | FY2025-26 average training hours rose sharply to 113.3 per employee through future-ready training initiatives | Integrated Annual Report details structured learning programs tied to AI-skilling and role readiness</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PwC Global Annual Review 2025</t>
+          <t>Infosys Integrated Annual Report 2024-25 and 2025-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -643,31 +653,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>https://www.capgemini.com</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=CAP</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.wipro.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=WIT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Average of 97.2 learning hours per employee in FY2025, including learning in the flow of work | ESG policy target: grow average learning hours per employee by 5% every year for lifelong learning | Learning &amp; Development careers page highlights structured upskilling paths as part of employee value proposition</t>
+          <t>publishes detailed training-hour and skilling metrics in its FY2025-26 Integrated Annual Report / Business Responsibility and Sustainability Report, following industry-standard IT-services disclosure practice | operates structured learning delivery via virtual instructor-led training, self-paced modules, and gamified learning journeys | ties learning investment to compliance and role-based training completion alongside technical/AI upskilling programs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Capgemini 2025 Universal Registration Document</t>
+          <t>Wipro Integrated Annual Report 2025-26 â€” exact FY26 training-hour figure not retrievable via search</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>HCL Technologies</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -675,31 +685,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>https://www.cognizant.com</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1058290/000105829026000008/ctsh-20251231.htm</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.hcltech.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=HCLTECH</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Synapse upskilling program commitment doubled in 2025 after hitting its original goal early; now targeting 2 million future workers upskilled by 2030 | In 2024, over 277,000 employees acquired at least one new skill via Cognizant's learning ecosystem, and 168,000+ associates completed generative AI training | Launched Cognizant Skillspring, an internal-proven talent transformation platform providing AI tools and role-redesign pathways</t>
+          <t>In FY25, HCLTech trained ~80% of employees in core skills, over 115,500 in digital skills, and 116,200+ in GenAI | Named internal learning programs include Career Shaper (talent transformation platform), AIvantage, BeRelevanT, CyberEdge, and AcceleraTor, plus a global mentorship program called MentorMe | 131,000+ employees completed behavioral/leadership development courses and MentorMe logged 61,000+ mentoring hours in FY25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cognizant FY2025 10-K (SEC EDGAR) and Cognizant Skillspring press materials</t>
+          <t>HCLTech Annual Report 2024-25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Alorica</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -707,31 +717,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>https://www.infosys.com</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=INFY</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.alorica.com</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FY2024-25 annual average training hours per employee reported at 71.35 | FY2025-26 average training hours rose sharply to 113.3 per employee through future-ready training initiatives | Integrated Annual Report details structured learning programs tied to AI-skilling and role readiness</t>
+          <t>Runs 'Alorica University'/Alorica Academy, a global leadership development platform covering new-employee onboarding, product training, skills coaching, and professional development | Approximately 80% of promotions are filled from within, reflecting internal career-pathing emphasis tied to its training programs | Offers paid training and tuition reimbursement as part of its employee benefits alongside open-access Academy courses</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Infosys Integrated Annual Report 2024-25 and 2025-26</t>
+          <t>Alorica careers site and Alorica Way fact sheet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Teleperformance</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -739,31 +744,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>https://www.wipro.com</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=WIT</t>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.teleperformance.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=TEP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>publishes detailed training-hour and skilling metrics in its FY2025-26 Integrated Annual Report / Business Responsibility and Sustainability Report, following industry-standard IT-services disclosure practice | operates structured learning delivery via virtual instructor-led training, self-paced modules, and gamified learning journeys | ties learning investment to compliance and role-based training completion alongside technical/AI upskilling programs</t>
+          <t>Operates 'TP University,' an internal learning platform/college-style program focused on embedding company culture and sharing best practices in customer experience management | In 2024, completed 60,000+ manager-level 'EI/AI expert' training programs as part of a global AI and emotional-intelligence skills initiative | Publishes detailed workforce training metrics annually in its Universal Registration Document (URD) filed with French regulators</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wipro Integrated Annual Report 2025-26 â€” exact FY26 training-hour figure not retrievable via search</t>
+          <t>Teleperformance Universal Registration Document 2024/2025</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HCL Technologies</t>
+          <t>Sutherland Global Services</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -771,31 +776,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>https://www.hcltech.com</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=HCLTECH</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.sutherlandglobal.com</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>In FY25, HCLTech trained ~80% of employees in core skills, over 115,500 in digital skills, and 116,200+ in GenAI | Named internal learning programs include Career Shaper (talent transformation platform), AIvantage, BeRelevanT, CyberEdge, and AcceleraTor, plus a global mentorship program called MentorMe | 131,000+ employees completed behavioral/leadership development courses and MentorMe logged 61,000+ mentoring hours in FY25</t>
+          <t>Runs an internal 'Center of Learning' delivering initial and ongoing leadership development training for employees | Offers international certification tracks in Technical (A+, N+, MCP) and Management (PMP, Six Sigma, COPC, ISO, BS7799, PCMM) streams | Over 38,000 employees across 19+ countries and 60+ global operation centers supported by these L&amp;D programs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HCLTech Annual Report 2024-25</t>
+          <t>Sutherland careers/training materials</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Syntel</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -803,26 +803,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>https://www.syntelinc.com</t>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.genpact.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1398659/000139865926000004/g-20251231.htm</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Syntel (acquired by Atos in 2018, brand discontinued) likely ran standard IT-services onboarding and technical certification tracks typical of Indian IT outsourcers of its era | probably offered structured new-hire training and internal promotion-driven career pathing consistent with its 'Talent Factory' HR branding reported around 2010-2012 | any company-specific L&amp;D branding or metrics from the Syntel era are no longer maintained or publicly trackable post-acquisition</t>
+          <t>Employees completed over 12.5 million learning hours in FY2025, averaging 89 hours per employee, via the proprietary 'Genome' reskilling platform | Delivered 5M+ hours of technology/AI skilling in 2025 (2.5x YoY increase) and grew AI talent to 7,000+ 'AI builders' and ~20,000 'AI practitioners' | Maintains named leadership pipelines (Global Operations Leadership Development, Leadership Direct); recognized by ATD in 2026 for AI-first workforce learning</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Limited/no current source â€” company defunct since 2018 Atos acquisition</t>
+          <t>Genpact FY2025 10-K (SEC)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Convergys</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -830,26 +835,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>https://www.convergys.com</t>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.exlservice.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1297989/000129798926000008/exls-20251231.htm</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Historically offered 2-4 weeks of classroom onboarding training depending on line of business, followed by on-the-job production floor training | In 2004 Convergys acquired e-learning provider DigitalThink for $120 million to expand workforce development/HRO training offerings | Partnered with Bellevue University to provide dedicated advisors enabling employees to pursue further education while employed</t>
+          <t>Operates a 'democratized learning ecosystem' combining AI-based content recommendations, curated libraries, peer learning groups, hands-on labs and supervisor dashboards | Runs named industry academies (e.g., EXL Healthcare Academy in Manila, expanding to India) delivering certifications and specialization tracks via blended learning | 10-K describes structured, career-linked learning paths from new hires to senior leadership, with dedicated AI/analytics/CX capability-building programs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Historical company records (pre-2018); Convergys absorbed into Concentrix/Synnex in 2018</t>
+          <t>EXL Service FY2025 10-K (SEC)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alorica</t>
+          <t>WNS Global Services</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -857,26 +867,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>https://www.alorica.com</t>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.wns.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=WNS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Runs 'Alorica University'/Alorica Academy, a global leadership development platform covering new-employee onboarding, product training, skills coaching, and professional development | Approximately 80% of promotions are filled from within, reflecting internal career-pathing emphasis tied to its training programs | Offers paid training and tuition reimbursement as part of its employee benefits alongside open-access Academy courses</t>
+          <t>Employees logged over 5 million learning hours in FY2024-25 per the company's fifth annual Corporate Sustainability Report | Workforce of 66,000+ globally is supported under an ESG pillar branded 'Enabling People to Outperform,' covering inclusion and future-ready skills development | Sustainability reporting aligned to GRI, SASB, and UN SDG standards, reflecting formalized tracking of L&amp;D metrics</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alorica careers site and Alorica Way fact sheet</t>
+          <t>WNS FY2024-25 Corporate Sustainability Report</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Teleperformance</t>
+          <t>Aon Hewitt</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -884,31 +899,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>https://www.teleperformance.com</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=TEP</t>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.aonhewitt.com</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Operates 'TP University,' an internal learning platform/college-style program focused on embedding company culture and sharing best practices in customer experience management | In 2024, completed 60,000+ manager-level 'EI/AI expert' training programs as part of a global AI and emotional-intelligence skills initiative | Publishes detailed workforce training metrics annually in its Universal Registration Document (URD) filed with French regulators</t>
+          <t>Aon Learning Center delivers HR-focused certification and leadership programs (HR Academy, Leadership Academy) that have trained 140,000+ professionals across 500+ global client organizations | Runs the 'Accelerate' program for early-career/individual-contributor colleagues, recognized as a Training Top 125 Best Practice | Company describes a broader learning curriculum from self-guided courses to advanced leadership development aligned to its 'Aon United' strategy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Teleperformance Universal Registration Document 2024/2025</t>
+          <t>aonlearningcenter.com, Training Top 125 feature</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sutherland Global Services</t>
+          <t>Mercer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -916,26 +926,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sutherlandglobal.com</t>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.mercer.com</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Runs an internal 'Center of Learning' delivering initial and ongoing leadership development training for employees | Offers international certification tracks in Technical (A+, N+, MCP) and Management (PMP, Six Sigma, COPC, ISO, BS7799, PCMM) streams | Over 38,000 employees across 19+ countries and 60+ global operation centers supported by these L&amp;D programs</t>
+          <t>Mercer is part of Marsh McLennan (MMC), which employed 90,000+ colleagues globally as of Dec 2024, ~30,500 in the Consulting segment that includes Mercer | MMC's Chief People Officer leads an enterprise people strategy covering training, development and engagement of talent, with oversight from the Compensation Committee | MMC directs investors to its ESG Report for detailed human-capital/training disclosures rather than the 10-K itself</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sutherland careers/training materials</t>
+          <t>Marsh &amp; McLennan Companies FY2024 10-K (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Towers Watson</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -943,31 +953,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>https://www.genpact.com</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1398659/000139865926000004/g-20251231.htm</t>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.towerswatson.com</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Employees completed over 12.5 million learning hours in FY2025, averaging 89 hours per employee, via the proprietary 'Genome' reskilling platform | Delivered 5M+ hours of technology/AI skilling in 2025 (2.5x YoY increase) and grew AI talent to 7,000+ 'AI builders' and ~20,000 'AI practitioners' | Maintains named leadership pipelines (Global Operations Leadership Development, Leadership Direct); recognized by ATD in 2026 for AI-first workforce learning</t>
+          <t>Towers Watson merged with Willis Group in 2016 to form Willis Towers Watson (WTW), which has 45,000+ employees across 140+ countries | WTW invests in structured training, mentorship and leadership-development programs plus technical skill-building workshops for associates at all levels | WTW's early-career apprenticeship program includes a fully funded professional qualification alongside on-the-job mentoring</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Genpact FY2025 10-K (SEC)</t>
+          <t>WTW careers site, post-merger successor to Towers Watson</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>A.T. Kearney</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -975,31 +980,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>https://www.exlservice.com</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1297989/000129798926000008/exls-20251231.htm</t>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.atkearney.com</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Operates a 'democratized learning ecosystem' combining AI-based content recommendations, curated libraries, peer learning groups, hands-on labs and supervisor dashboards | Runs named industry academies (e.g., EXL Healthcare Academy in Manila, expanding to India) delivering certifications and specialization tracks via blended learning | 10-K describes structured, career-linked learning paths from new hires to senior leadership, with dedicated AI/analytics/CX capability-building programs</t>
+          <t>Kearney runs an end-to-end curriculum for consultants combining in-person programs, live virtual 'cafe conversations,' and self-paced digital learning | Junior consultants build foundational consulting/technical skills plus electives for leadership prep before transitioning to manager | Kearney's Global Mobility program lets consultants transfer to international offices or staff on global engagements as a development tool</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EXL Service FY2025 10-K (SEC)</t>
+          <t>Kearney careers site (kearney.com)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WNS Global Services</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1007,31 +1007,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>https://www.wns.com</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=WNS</t>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.boozallen.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1443646/000162828026037521/bah-20260331.htm</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Employees logged over 5 million learning hours in FY2024-25 per the company's fifth annual Corporate Sustainability Report | Workforce of 66,000+ globally is supported under an ESG pillar branded 'Enabling People to Outperform,' covering inclusion and future-ready skills development | Sustainability reporting aligned to GRI, SASB, and UN SDG standards, reflecting formalized tracking of L&amp;D metrics</t>
+          <t>Booz Allen Hamilton (35,800 employees as of March 2025, 88% hold a bachelor's degree or higher) runs upskilling programs with hands-on learning, in-house training, formal badging and certificate programs | Its Technical Experience Groups (TXGs) build technical acumen and mentor/mentee relationships tied to skill enhancement and retention | In 2022 Booz Allen built an Integrated Technical Talent System connecting Talent Development, Acquisition and Mobility</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>WNS FY2024-25 Corporate Sustainability Report</t>
+          <t>Booz Allen Hamilton FY2025 10-K human capital section</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aon Hewitt</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1039,26 +1039,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>https://www.aonhewitt.com</t>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.mckinsey.com</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aon Learning Center delivers HR-focused certification and leadership programs (HR Academy, Leadership Academy) that have trained 140,000+ professionals across 500+ global client organizations | Runs the 'Accelerate' program for early-career/individual-contributor colleagues, recognized as a Training Top 125 Best Practice | Company describes a broader learning curriculum from self-guided courses to advanced leadership development aligned to its 'Aon United' strategy</t>
+          <t>McKinsey Academy (launched 2014) now offers 30+ external capability-building programs and has won 40+ Brandon Hall HCM Excellence Awards over seven years | Its free Connected Leaders Academy has engaged 100,000+ participants from 1,300+ organizations since 2020, and McKinsey Forward is a free multi-week digital program open to individuals at any career stage | Internally, McKinsey emphasizes continuous learning via mentorship and diverse project staffing to build leadership and problem-solving skills</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>aonlearningcenter.com, Training Top 125 feature</t>
+          <t>McKinsey &amp; Company careers/McKinsey Academy pages</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mercer</t>
+          <t>Boston Consulting Group</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1066,26 +1066,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>https://www.mercer.com</t>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.bcg.com</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mercer is part of Marsh McLennan (MMC), which employed 90,000+ colleagues globally as of Dec 2024, ~30,500 in the Consulting segment that includes Mercer | MMC's Chief People Officer leads an enterprise people strategy covering training, development and engagement of talent, with oversight from the Compensation Committee | MMC directs investors to its ESG Report for detailed human-capital/training disclosures rather than the 10-K itself</t>
+          <t>BCG U, its organizational-development/capability platform, compressed learning content from 150+ hours of academic material down to 15 hours of bite-sized digital learning | BCG launched a Climate &amp; Sustainability Academy to upskill staff on sustainability topics, and its RISE/RISE for Business programs help individuals reskill into digital roles | Internally BCG combines formal training with apprenticeship-style coaching and mentorship for consultant development</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Marsh &amp; McLennan Companies FY2024 10-K (SEC EDGAR)</t>
+          <t>BCG capabilities/careers pages</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Towers Watson</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1093,26 +1093,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>https://www.towerswatson.com</t>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.bain.com</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Towers Watson merged with Willis Group in 2016 to form Willis Towers Watson (WTW), which has 45,000+ employees across 140+ countries | WTW invests in structured training, mentorship and leadership-development programs plus technical skill-building workshops for associates at all levels | WTW's early-career apprenticeship program includes a fully funded professional qualification alongside on-the-job mentoring</t>
+          <t>Bain operates an apprenticeship-style learning model with structured milestone offsites (e.g., in Berlin, Miami, Singapore) combining peer training with senior-leader-led sessions | Every consultant gets one-on-one mentor coaching and a personalized learning pathway managed by Bain's dedicated L&amp;D team | Bain funds graduate studies for high performers who return after completing programs, and supports externships/global transfers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>WTW careers site, post-merger successor to Towers Watson</t>
+          <t>Bain &amp; Company careers site</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A.T. Kearney</t>
+          <t>Oliver Wyman</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1120,26 +1120,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>https://www.atkearney.com</t>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.oliverwyman.com</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kearney runs an end-to-end curriculum for consultants combining in-person programs, live virtual 'cafe conversations,' and self-paced digital learning | Junior consultants build foundational consulting/technical skills plus electives for leadership prep before transitioning to manager | Kearney's Global Mobility program lets consultants transfer to international offices or staff on global engagements as a development tool</t>
+          <t>Oliver Wyman (part of Marsh McLennan) runs a 12-month Consultant Development Program (CDP) giving new hires hands-on project experience from day one | The firm pairs employees with mentors/coaches and offers structured training curriculums with no artificial barriers to advancement | Its FlexOW program lets consultants pursue sabbaticals, externships and secondments to nonprofits or sister MMC firms as part of career development</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kearney careers site (kearney.com)</t>
+          <t>Oliver Wyman careers site</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1147,31 +1147,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>https://www.boozallen.com</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1443646/000162828026037521/bah-20260331.htm</t>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.protiviti.com</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton (35,800 employees as of March 2025, 88% hold a bachelor's degree or higher) runs upskilling programs with hands-on learning, in-house training, formal badging and certificate programs | Its Technical Experience Groups (TXGs) build technical acumen and mentor/mentee relationships tied to skill enhancement and retention | In 2022 Booz Allen built an Integrated Technical Talent System connecting Talent Development, Acquisition and Mobility</t>
+          <t>Protiviti (Robert Half subsidiary, ~7,100 employees as of Dec 2025) assigns every employee a career adviser and pays for select recognized professional certifications | Protiviti runs milestone learning events to prepare staff for promotion to higher levels | Parent Robert Half reports development/training as a key retention and engagement lever, offering new-hire, tenured-employee and leadership-specific programs plus mentorship</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton FY2025 10-K human capital section</t>
+          <t>Robert Half Inc. FY2025 10-K (SEC EDGAR) human capital section</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Grant Thornton</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1179,26 +1174,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>https://www.mckinsey.com</t>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.grantthornton.com</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>McKinsey Academy (launched 2014) now offers 30+ external capability-building programs and has won 40+ Brandon Hall HCM Excellence Awards over seven years | Its free Connected Leaders Academy has engaged 100,000+ participants from 1,300+ organizations since 2020, and McKinsey Forward is a free multi-week digital program open to individuals at any career stage | Internally, McKinsey emphasizes continuous learning via mentorship and diverse project staffing to build leadership and problem-solving skills</t>
+          <t>Grant Thornton won gold ('Best Program for Upskilling Employees') and silver ('Best Blended Learning Program') 2023 Brandon Hall Group awards for its digital badging/Career Compass skills framework and Manager Development Program | All client-facing employees must accrue annual CPE hours, supported via licensed providers (LinkedIn Learning, Becker, PSI, AICPA) plus firm-generated content | Its Manager Development Program (MDP) auto-enrolls every employee promoted into a manager role</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company careers/McKinsey Academy pages</t>
+          <t>Grant Thornton press release and careers L&amp;D page</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Boston Consulting Group</t>
+          <t>RSM US</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1206,26 +1201,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>https://www.bcg.com</t>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.rsmus.com</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BCG U, its organizational-development/capability platform, compressed learning content from 150+ hours of academic material down to 15 hours of bite-sized digital learning | BCG launched a Climate &amp; Sustainability Academy to upskill staff on sustainability topics, and its RISE/RISE for Business programs help individuals reskill into digital roles | Internally BCG combines formal training with apprenticeship-style coaching and mentorship for consultant development</t>
+          <t>RSM US provides curated exam-prep learning paths for IT/security certifications (CISA, CISSP, CCSP, CompTIA) alongside hundreds of RSM-developed and partner training courses | RSM strongly encourages associates on the CPA track to license early, reimbursing Becker CPA review materials plus exam and application fees | New campus hires go through the 'Starting Your Career at RSM Experience' onboarding/development program tied to a formal career-advisor framework</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BCG capabilities/careers pages</t>
+          <t>RSM US careers site</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>BDO USA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1233,26 +1228,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>https://www.bain.com</t>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.bdo.com</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bain operates an apprenticeship-style learning model with structured milestone offsites (e.g., in Berlin, Miami, Singapore) combining peer training with senior-leader-led sessions | Every consultant gets one-on-one mentor coaching and a personalized learning pathway managed by Bain's dedicated L&amp;D team | Bain funds graduate studies for high performers who return after completing programs, and supports externships/global transfers</t>
+          <t>BDO USA reimburses CPA exam costs, study time and course materials, with training checklists tied to each employee's level and business line | Its 'Exceptional &amp; Engaged Leaders' development track begins at the earliest career stage and includes milestone leadership programs | BDO pairs every new hire with a mentor on day one, plus a broader mentorship/advisory program connecting less-experienced staff with senior professionals</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bain &amp; Company careers site</t>
+          <t>BDO USA careers site</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Oliver Wyman</t>
+          <t>Crowe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1260,26 +1255,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>https://www.oliverwyman.com</t>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.crowe.com</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oliver Wyman (part of Marsh McLennan) runs a 12-month Consultant Development Program (CDP) giving new hires hands-on project experience from day one | The firm pairs employees with mentors/coaches and offers structured training curriculums with no artificial barriers to advancement | Its FlexOW program lets consultants pursue sabbaticals, externships and secondments to nonprofits or sister MMC firms as part of career development</t>
+          <t>Crowe LLP runs 'Crowe University,' a structured curriculum with business-unit-specific 'colleges' plus cross-functional colleges for industry specialization, technology and leadership skills | Crowe reimburses licensing/certification costs including CPA exam fees and covers continuing professional education (CPE) credits | Every employee meets regularly with an assigned career coach to set learning plans and career goals</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oliver Wyman careers site</t>
+          <t>Crowe LLP careers site</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>DHG (Dixon Hughes Goodman)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1287,26 +1282,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>https://www.protiviti.com</t>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.dhg.com</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Protiviti (Robert Half subsidiary, ~7,100 employees as of Dec 2025) assigns every employee a career adviser and pays for select recognized professional certifications | Protiviti runs milestone learning events to prepare staff for promotion to higher levels | Parent Robert Half reports development/training as a key retention and engagement lever, offering new-hire, tenured-employee and leadership-specific programs plus mentorship</t>
+          <t>DHG (Dixon Hughes Goodman) merged into Forvis in June 2022 and no longer operates independently or publishes standalone training disclosures | prior to the merger, DHG offered typical mid-tier accounting-firm CPA exam support, mentoring and CPE programs consistent with industry norms | legacy DHG training programs were folded into Forvis Mazars' current learning and development framework post-merger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Robert Half Inc. FY2025 10-K (SEC EDGAR) human capital section</t>
+          <t>Company history via Forvis Mazars; firm defunct since 2022</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Grant Thornton</t>
+          <t>Forrester</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1314,26 +1309,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>https://www.grantthornton.com</t>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.forrester.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1023313/000119312526105114/forr-20251231.htm</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Grant Thornton won gold ('Best Program for Upskilling Employees') and silver ('Best Blended Learning Program') 2023 Brandon Hall Group awards for its digital badging/Career Compass skills framework and Manager Development Program | All client-facing employees must accrue annual CPE hours, supported via licensed providers (LinkedIn Learning, Becker, PSI, AICPA) plus firm-generated content | Its Manager Development Program (MDP) auto-enrolls every employee promoted into a manager role</t>
+          <t>New Forrester employees complete a three-day onboarding covering the company's customer-obsessed strategy, products, culture and values | Forrester offers ongoing training including a formal Leadership Development Program plus courses on resilience and change | Forrester separately monetizes a 'Forrester Training &amp; Certification' analyst-methodology curriculum for external clients, run alongside internal L&amp;D efforts</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grant Thornton press release and careers L&amp;D page</t>
+          <t>Forrester Research 10-K human capital disclosures (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RSM US</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1341,26 +1341,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>https://www.rsmus.com</t>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.gartner.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/749251/000074925126000112/it-20251231.htm</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RSM US provides curated exam-prep learning paths for IT/security certifications (CISA, CISSP, CCSP, CompTIA) alongside hundreds of RSM-developed and partner training courses | RSM strongly encourages associates on the CPA track to license early, reimbursing Becker CPA review materials plus exam and application fees | New campus hires go through the 'Starting Your Career at RSM Experience' onboarding/development program tied to a formal career-advisor framework</t>
+          <t>Gartner's internal learning platform 'GartnerYou' offered approximately 26,000 learning resources in 2024, with over 410,000 completions globally that year | Sales and Research &amp; Advisory staff (~45% of Gartner's global workforce) go through formal dedicated onboarding and leadership training programs | Gartner runs dedicated DEI learning modules covering bias, empathy and inclusive leadership alongside rotational development programs</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RSM US careers site</t>
+          <t>Gartner Inc. 10-K human capital section (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BDO USA</t>
+          <t>IDC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1368,26 +1373,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>https://www.bdo.com</t>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.idc.com</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BDO USA reimburses CPA exam costs, study time and course materials, with training checklists tied to each employee's level and business line | Its 'Exceptional &amp; Engaged Leaders' development track begins at the earliest career stage and includes milestone leadership programs | BDO pairs every new hire with a mentor on day one, plus a broader mentorship/advisory program connecting less-experienced staff with senior professionals</t>
+          <t>IDC (part of Blackstone-owned IDG) publishes Fall and Winter/Spring internal training calendars covering professional, functional and wellness classes | Research analysts get ongoing skills training including sessions on writing, grammar and forecasting; sales staff get training on cross-selling, negotiating and presentation skills | IDC's mentor program has run 15+ years connecting mentees and mentors across departments for career development</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>BDO USA careers site</t>
+          <t>IDC careers page (idc.com/about/careers)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Crowe</t>
+          <t>Alvarez &amp; Marsal</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1395,26 +1400,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>https://www.crowe.com</t>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.alvarezandmarsal.com</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crowe LLP runs 'Crowe University,' a structured curriculum with business-unit-specific 'colleges' plus cross-functional colleges for industry specialization, technology and leadership skills | Crowe reimburses licensing/certification costs including CPA exam fees and covers continuing professional education (CPE) credits | Every employee meets regularly with an assigned career coach to set learning plans and career goals</t>
+          <t>Alvarez &amp; Marsal's new-hire onboarding is a two-week program covering firm introduction, ways of working and technical skills, followed by 50+ additional courses available annually | A&amp;M University is an annual firmwide gathering for professionals across business units focused on skills, networking and culture | A&amp;M offers tuition reimbursement and a Competency Guide mapping key skills to each career level, plus a formal mentoring program</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crowe LLP careers site</t>
+          <t>Alvarez &amp; Marsal careers/training page</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DHG (Dixon Hughes Goodman)</t>
+          <t>Aon plc</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1422,26 +1427,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>https://www.dhg.com</t>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.aon.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/315293/000162828026008116/aon-20251231.htm</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DHG (Dixon Hughes Goodman) merged into Forvis in June 2022 and no longer operates independently or publishes standalone training disclosures | prior to the merger, DHG offered typical mid-tier accounting-firm CPA exam support, mentoring and CPE programs consistent with industry norms | legacy DHG training programs were folded into Forvis Mazars' current learning and development framework post-merger</t>
+          <t>Aon University offers self-guided courses through advanced learning programs aligned to the 'Aon United Blueprint' and Inclusive People Leader strategy | Aon delivers learning primarily through virtual/immersive formats given its largely distributed global workforce | Aon's 10-K human capital section describes curricula tailored to colleagues' career stage goals and developmental needs across all levels</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Company history via Forvis Mazars; firm defunct since 2022</t>
+          <t>Aon plc 10-K human capital section (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Forrester</t>
+          <t>Avanade Inc.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1449,31 +1459,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>https://www.forrester.com</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1023313/000119312526105114/forr-20251231.htm</t>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.avanade.com</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>New Forrester employees complete a three-day onboarding covering the company's customer-obsessed strategy, products, culture and values | Forrester offers ongoing training including a formal Leadership Development Program plus courses on resilience and change | Forrester separately monetizes a 'Forrester Training &amp; Certification' analyst-methodology curriculum for external clients, run alongside internal L&amp;D efforts</t>
+          <t>Avanade (Accenture/Microsoft joint venture) mandates a minimum of 80 hours per year of training and paid certifications per employee | Employees are pushed toward Microsoft Certifications, with training delivered via in-person, virtual instructor-led and self-paced formats | Avanade's 'Limitless Learning' program pairs staff with experienced mentors alongside its formal certification tracks</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Forrester Research 10-K human capital disclosures (SEC EDGAR)</t>
+          <t>Avanade careers page</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>CGI Inc.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1481,31 +1486,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>https://www.gartner.com</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/749251/000074925126000112/it-20251231.htm</t>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.cgi.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=GIB</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gartner's internal learning platform 'GartnerYou' offered approximately 26,000 learning resources in 2024, with over 410,000 completions globally that year | Sales and Research &amp; Advisory staff (~45% of Gartner's global workforce) go through formal dedicated onboarding and leadership training programs | Gartner runs dedicated DEI learning modules covering bias, empathy and inclusive leadership alongside rotational development programs</t>
+          <t>Global AI learning strategy earned Skillsoft's 'Program of the Year' and 'Impact' awards for CGI | Offers structured career development combining stretch project assignments, job shadowing, coaching, mentoring, and access to leadership/core-competency programs | Workforce of roughly 94,000 consultants and professionals worldwide (as of Sept 2025) supported by ongoing digital-skills reskilling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gartner Inc. 10-K human capital section (SEC EDGAR)</t>
+          <t>CGI.com Learning &amp; Development page; CGI 2025 Annual Report</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IDC</t>
+          <t>Cognizant Technology Solutions US Corporation</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1513,26 +1518,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>https://www.idc.com</t>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.cognizant.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1058290/000105829026000008/ctsh-20251231.htm</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IDC (part of Blackstone-owned IDG) publishes Fall and Winter/Spring internal training calendars covering professional, functional and wellness classes | Research analysts get ongoing skills training including sessions on writing, grammar and forecasting; sales staff get training on cross-selling, negotiating and presentation skills | IDC's mentor program has run 15+ years connecting mentees and mentors across departments for career development</t>
+          <t>More than 277,000 employees acquired at least one new skill through Cognizant's learning ecosystem in 2024 | Upskilled over 330,000 associates on Generative AI via 1,000+ learning programs between July 2023 and end of 2025, partnering with Google, Microsoft, Anthropic, and NVIDIA | Cognizant's Synapse initiative has invested $70M since 2018 supporting 70 global skilling organizations, with a 2025 commitment doubling the program to target upskilling 2 million workers by 2030</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>IDC careers page (idc.com/about/careers)</t>
+          <t>Cognizant 10-K (FY2025) and Synapse initiative press materials</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alvarez &amp; Marsal</t>
+          <t>Convergys Corporation</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1540,26 +1550,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>https://www.alvarezandmarsal.com</t>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.convergys.com</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alvarez &amp; Marsal's new-hire onboarding is a two-week program covering firm introduction, ways of working and technical skills, followed by 50+ additional courses available annually | A&amp;M University is an annual firmwide gathering for professionals across business units focused on skills, networking and culture | A&amp;M offers tuition reimbursement and a Competency Guide mapping key skills to each career level, plus a formal mentoring program</t>
+          <t>as a BPO/call-center operator (acquired by Synnex/Concentrix in 2018 and now defunct as a standalone entity), Convergys would have run structured agent-training and quality-certification programs typical of the customer-care outsourcing industry | Historically acquired DigitalThink, a San Francisco e-learning provider, for $120 million in 2004 to build out workforce e-learning/training platforms for clients | Convergys Philippines was named 'BPO Employer of the Year' in 2012, reflecting recognized training/development practices across its 26,000-employee Philippine operation</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Alvarez &amp; Marsal careers/training page</t>
+          <t>Company history (defunct post-2018 acquisition, no current filings)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Aon plc</t>
+          <t>Deloitte Consulting LLP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1567,31 +1577,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>https://www.aon.com</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/315293/000162828026008116/aon-20251231.htm</t>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.deloitte.com</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aon University offers self-guided courses through advanced learning programs aligned to the 'Aon United Blueprint' and Inclusive People Leader strategy | Aon delivers learning primarily through virtual/immersive formats given its largely distributed global workforce | Aon's 10-K human capital section describes curricula tailored to colleagues' career stage goals and developmental needs across all levels</t>
+          <t>FY2025 Learning &amp; Development direct investment exceeded $673 million globally, delivering over 21 million formal training hours | Project 120, a $1.4 billion investment in Deloitte US's learning transformation, has already delivered 1+ million hours of AI-focused training | Deloitte University (DU), the firm's flagship leadership-development campus network, has operated since 2011 across facilities in the Americas, Europe, and Asia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aon plc 10-K human capital section (SEC EDGAR)</t>
+          <t>Deloitte 2025 Global Impact Report / Project 120 press release</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Avanade Inc.</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1599,26 +1604,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>https://www.avanade.com</t>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.dxc.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1688568/000168856826000022/dxc-20260331.htm</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Avanade (Accenture/Microsoft joint venture) mandates a minimum of 80 hours per year of training and paid certifications per employee | Employees are pushed toward Microsoft Certifications, with training delivered via in-person, virtual instructor-led and self-paced formats | Avanade's 'Limitless Learning' program pairs staff with experienced mentors alongside its formal certification tracks</t>
+          <t>Operates a global learning management ecosystem offering hundreds of learning programs plus a formal career development system, described in its 10-K as a strategic investment in the workforce | Promotes a self-directed learning culture letting employees choose pace and format of training | Frames professional development as both a corporate-responsibility commitment and a retention/engagement strategy in SEC filings</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Avanade careers page</t>
+          <t>DXC Technology 10-K (FY2025)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCG (Boston Consulting Group)</t>
+          <t>Eliassen Group</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1626,26 +1636,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>https://www.bcg.com</t>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.eliassen.com</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>BCG University (BCG U) redesigned its core curriculum, cutting dense academic content from 150+ hours down to 15 hours of bite-sized, digestible modules | Offers a comprehensive online training catalog spanning tech-product skills to leadership development so consultants can personalize their learning journey | Runs the RISE by BCG academy (RISE 2.0) as a dedicated capability-building platform for talent development</t>
+          <t>Runs a formal Mentorship Program pairing consultants/employees with mentors for monthly targeted skill-development and career-growth sessions | New hires go through a structured onboarding training program at Eliassen's Wakefield, MA headquarters covering sales/recruiting and industry fundamentals | Offers Agile/Scrum@Scale training courses and a Consultant Advocate Program providing ongoing 24/7 professional support to placed consultants</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BCG.com / BCG Careers / RISE academy site</t>
+          <t>Eliassen Group careers site, employee reviews</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Capgemini US LLC</t>
+          <t>Ernst &amp; Young LLP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1653,26 +1663,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>https://www.capgemini.com/us-en/</t>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.ey.com</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ESG target: average 70 learning hours per employee per year, delivered via Capgemini University (self-paced learning, dedicated programs, web-based and face-to-face training) | Additional ESG target to grow average learning hours per employee by 5% every year | Disclosed annually in Capgemini's Universal Registration Document filed with the AMF (Euronext Paris)</t>
+          <t>Invested $300 million in formal employee training in a recent fiscal year, generating 20 million learning hours (average 59 hours per person) | EY's 2025 Work Reimagined Survey found staff receiving 81+ hours of annual AI training reported productivity gains nearly double the median | Offers a dedicated Learning &amp; Development advisory practice and internal learning-technology platforms tied to retention outcomes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Capgemini 2024/2025 Universal Registration Document</t>
+          <t>EY Global Review / EY Value Realized 2025 report</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CGI Inc.</t>
+          <t>FTI Consulting, Inc.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1680,31 +1690,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>https://www.cgi.com</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=GIB</t>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.fticonsulting.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/887936/000088793626000013/fcn-20251231.htm</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Global AI learning strategy earned Skillsoft's 'Program of the Year' and 'Impact' awards for CGI | Offers structured career development combining stretch project assignments, job shadowing, coaching, mentoring, and access to leadership/core-competency programs | Workforce of roughly 94,000 consultants and professionals worldwide (as of Sept 2025) supported by ongoing digital-skills reskilling</t>
+          <t>Robust Talent Development program spans onboarding, promotion-readiness training, and leadership-readiness programs for senior/managing director tracks, per its 10-K | Supplements formal training with self-directed e-learning and financially supports employees completing professional qualifications | Runs FTI WIN, a worldwide diversity initiative offering structured professional development and mentorship for women in consulting</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CGI.com Learning &amp; Development page; CGI 2025 Annual Report</t>
+          <t>FTI Consulting 10-K (FY2025)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions US Corporation</t>
+          <t>Huron Consulting Group Inc.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1712,31 +1722,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>https://www.cognizant.com</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1058290/000105829026000008/ctsh-20251231.htm</t>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.huronconsultinggroup.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1289848/000162828026011093/hurn-20251231.htm</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>More than 277,000 employees acquired at least one new skill through Cognizant's learning ecosystem in 2024 | Upskilled over 330,000 associates on Generative AI via 1,000+ learning programs between July 2023 and end of 2025, partnering with Google, Microsoft, Anthropic, and NVIDIA | Cognizant's Synapse initiative has invested $70M since 2018 supporting 70 global skilling organizations, with a 2025 commitment doubling the program to target upskilling 2 million workers by 2030</t>
+          <t>Offers year-long 'Milestone' development programs for recently promoted employees plus dedicated leadership-development programs for senior director/managing director tracks | Provides continuing education via classroom training, online courses, and webinars, and supports employees pursuing outside certifications and advanced degrees | Matches employees with internal performance coaches and mentors to guide career growth and skills certification</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cognizant 10-K (FY2025) and Synapse initiative press materials</t>
+          <t>Huron Consulting Group 10-K filings</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Convergys Corporation</t>
+          <t>Insight Enterprises, Inc.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1744,26 +1754,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>https://www.convergys.com</t>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.insight.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/932696/000093269626000007/nsit-20251231.htm</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>as a BPO/call-center operator (acquired by Synnex/Concentrix in 2018 and now defunct as a standalone entity), Convergys would have run structured agent-training and quality-certification programs typical of the customer-care outsourcing industry | Historically acquired DigitalThink, a San Francisco e-learning provider, for $120 million in 2004 to build out workforce e-learning/training platforms for clients | Convergys Philippines was named 'BPO Employer of the Year' in 2012, reflecting recognized training/development practices across its 26,000-employee Philippine operation</t>
+          <t>Maintains an ongoing internal/external training program covering new-hire orientation, sales training, technical/product training, and management development, per its 10-K | Leadership training centers on a 'Leadership Commitments' framework emphasizing clarity, inspiration, thought leadership, and results | Offers employees professional certification opportunities and tuition reimbursement for eligible staff</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Company history (defunct post-2018 acquisition, no current filings)</t>
+          <t>Insight Enterprises 10-K filings</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deloitte Consulting LLP</t>
+          <t>ISG (Information Services Group)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1771,26 +1786,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>https://www.deloitte.com</t>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.isg-one.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1371489/000110465926024573/iii-20251231x10k.htm</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FY2025 Learning &amp; Development direct investment exceeded $673 million globally, delivering over 21 million formal training hours | Project 120, a $1.4 billion investment in Deloitte US's learning transformation, has already delivered 1+ million hours of AI-focused training | Deloitte University (DU), the firm's flagship leadership-development campus network, has operated since 2011 across facilities in the Americas, Europe, and Asia</t>
+          <t>ISG Academy is the firm's global learning and development program covering industry/functional topics, leadership, certifications, and technical skills | In 2020, employees completed nearly 20,000 courses and logged 55,000+ learning hours; in 2021, 16,800+ courses and 31,000+ hours | Learning is bundled under the broader 'ISG WorkLife' set of Next-Gen HR programs aimed at talent attraction and retention</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deloitte 2025 Global Impact Report / Project 120 press release</t>
+          <t>ISG (Information Services Group) 10-K disclosures and ISG WorkLife program materials</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>JLL (Jones Lang LaSalle Incorporated)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1798,31 +1818,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>https://www.dxc.com</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1688568/000168856826000022/dxc-20260331.htm</t>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.us.jll.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1037976/000103797626000037/jll-20251231.htm</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Operates a global learning management ecosystem offering hundreds of learning programs plus a formal career development system, described in its 10-K as a strategic investment in the workforce | Promotes a self-directed learning culture letting employees choose pace and format of training | Frames professional development as both a corporate-responsibility commitment and a retention/engagement strategy in SEC filings</t>
+          <t>More than 45,000 JLL employees completed a combined 127,000 dedicated sustainability learning courses in 2022/2023 | Formed a dedicated Sustainability Learning &amp; Development team in July 2022 to build sustainability skills across its ~100,000-person workforce, supporting its 2030 net-zero goal | Maintains a library of over 4,000 learning modules spanning live and e-learning formats company-wide</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>DXC Technology 10-K (FY2025)</t>
+          <t>JLL 10-K / Training APEX Award coverage</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Eliassen Group</t>
+          <t>KPMG LLP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1830,26 +1850,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>https://www.eliassen.com</t>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.kpmg.com</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Runs a formal Mentorship Program pairing consultants/employees with mentors for monthly targeted skill-development and career-growth sessions | New hires go through a structured onboarding training program at Eliassen's Wakefield, MA headquarters covering sales/recruiting and industry fundamentals | Offers Agile/Scrum@Scale training courses and a Consultant Advocate Program providing ongoing 24/7 professional support to placed consultants</t>
+          <t>KPMG Lakehouse campus in Lake Nona, FL delivers over 1 million hours of in-person professional development annually for U.S. employees and partners | Advisory professionals are required to complete a minimum of 25 hours of learning each year | Offers a 'Learning as a Service' (LaaS) capability and extensive digital learning platforms covering leadership, data, and AI-era skills</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Eliassen Group careers site, employee reviews</t>
+          <t>KPMG.com Learning &amp; Development Services pages</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ernst &amp; Young LLP</t>
+          <t>Leidos Holdings, Inc.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1857,26 +1877,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>https://www.ey.com</t>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.leidos.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1336920/000133692026000030/ldos-20260102.htm</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Invested $300 million in formal employee training in a recent fiscal year, generating 20 million learning hours (average 59 hours per person) | EY's 2025 Work Reimagined Survey found staff receiving 81+ hours of annual AI training reported productivity gains nearly double the median | Offers a dedicated Learning &amp; Development advisory practice and internal learning-technology platforms tied to retention outcomes</t>
+          <t>Offers formal certification-prep programs for the Project Management Institute (PMI/PMP) and International Council on Systems Engineering, plus resources for 95+ other industry-standard professional/technical certifications | Provides tuition assistance to all U.S. full-time employees at accredited universities | Runs the 'Leidos Leadership' program along with targeted development for managers and executive leaders</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>EY Global Review / EY Value Realized 2025 report</t>
+          <t>Leidos Holdings 10-K (FY2026)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FTI Consulting, Inc.</t>
+          <t>LTI (Larsen &amp; Toubro Infotech)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1884,31 +1909,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>https://www.fticonsulting.com</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/887936/000088793626000013/fcn-20251231.htm</t>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.lntinfotech.com</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Robust Talent Development program spans onboarding, promotion-readiness training, and leadership-readiness programs for senior/managing director tracks, per its 10-K | Supplements formal training with self-directed e-learning and financially supports employees completing professional qualifications | Runs FTI WIN, a worldwide diversity initiative offering structured professional development and mentorship for women in consulting</t>
+          <t>Runs 'Learn Grow Lead' and Manager Development programs to build a pipeline of future-ready leaders, supplemented by AI-personalized career and learning pathways | Historically (FY2020-21 as LTI) delivered 2,500+ learning programs including 344+ competency-based behavioral/leadership and job-family learning tracks | Reports learning and development metrics annually in the 'Social' section of the LTIMindtree Integrated Annual Report</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FTI Consulting 10-K (FY2025)</t>
+          <t>LTIMindtree Integrated Annual Report (2024-25)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Grant Thornton LLP</t>
+          <t>ManpowerGroup Inc.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1916,26 +1936,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>https://www.grantthornton.com</t>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.manpowergroup.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/871763/000119312526064113/man-20251231.htm</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Invested Â£1 million in a 'data and digital mindset' transformation training programme for UK employees | Won gold (Best Program for Upskilling Employees) and silver (Best Blended Learning Program) at Brandon Hall Group awards | Runs Fullstax, an internal program building emerging-technology skills, alongside tiered leadership programs</t>
+          <t>ManpowerGroup's MyPath program has scaled to more than 301,000 associates for career pathways and upskilling into growth roles | Experis Academy has trained more than 4,500 developers and bridged skills gaps for 170+ tech companies across ~20 countries through 2025 | Future Leaders Program has graduated 1,166 employees since 2019, with 121 enrolled in 2025</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HR Grapevine; Grant Thornton press releases</t>
+          <t>ManpowerGroup FY2025 10-K (SEC) and 2024-2025 Sustainability Report</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HCL America Inc.</t>
+          <t>NTT DATA Services</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1943,26 +1968,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>https://www.hcltech.com</t>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.nttdataservices.com</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FY2022-23: invested 9.4 million person-hours in training, with 70,000+ employees trained in digital skills and 150,000+ in core skills | FY2024-25: 115,500+ employees trained in digital skills, 116,200+ trained in GenAI, and 131,000+ completed behavioral/leadership development courses | Learning framework spans cloud, engineering, 5G/6G, and ESG-linked technology skill-building</t>
+          <t>NTT DATA is training its ~200,000 global employees in foundational generative AI skills, with a goal of 30,000+ certified higher-level GenAI practitioners by FY2026 | Delivers training via its GenAI Academy, a multi-tiered self-paced learning, hands-on-lab program | Offers structured, tailored career-progression development paths from entry-level through management/leadership roles</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HCLTech Annual Report 2023 and 2025</t>
+          <t>NTT DATA Group press releases and corporate sustainability/HR pages</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Huron Consulting Group Inc.</t>
+          <t>RGP (Resources Global Professionals)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1970,31 +1995,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>https://www.huronconsultinggroup.com</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1289848/000162828026011093/hurn-20251231.htm</t>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.rgp.com</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Offers year-long 'Milestone' development programs for recently promoted employees plus dedicated leadership-development programs for senior director/managing director tracks | Provides continuing education via classroom training, online courses, and webinars, and supports employees pursuing outside certifications and advanced degrees | Matches employees with internal performance coaches and mentors to guide career growth and skills certification</t>
+          <t>Resources Connection (parent of RGP) 10-K human capital section emphasizes leadership development programs and mentorship as part of retention strategy | Culture and career-development investment centers on hybrid work, wellness, and employee wellbeing initiatives | Company frames talent development as a core differentiator in its flexible/on-demand consulting workforce model</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Huron Consulting Group 10-K filings</t>
+          <t>Resources Connection Inc. FY2025 10-K (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IBM Global Business Services</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2002,31 +2022,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t>https://www.ibm.com</t>
-        </is>
-      </c>
-      <c r="D55" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/51143/000005114326000010/ibm-20251231.htm</t>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.slalom.com</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spends roughly $600 million annually on employee training and development | Requires all employees to complete at least 40 hours of learning per year on its digital learning platform, with average completion around 85 hours | Runs a U.S. apprenticeship program that has hired about 1,000 apprentices, with 90%+ converting to full-time roles; committed to skilling 30 million people globally by 2030</t>
+          <t>Slalom (13,000+ team members) provides a free internal online learning library plus funding for third-party trainings and certifications | Runs a 'Road to Readiness' program guiding specific roles toward relevant AWS certifications | Offers multi-session, cohort-based offsite leadership-development programs for anyone in a people- or practice-management role</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>IBM 10-K (FY2025) and IBM Skills Development</t>
+          <t>Slalom careers site and AWS Training &amp; Certification blog</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Insight Enterprises, Inc.</t>
+          <t>Syntel Inc.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2034,31 +2049,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>https://www.insight.com</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/932696/000093269626000007/nsit-20251231.htm</t>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.syntelinc.com</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Maintains an ongoing internal/external training program covering new-hire orientation, sales training, technical/product training, and management development, per its 10-K | Leadership training centers on a 'Leadership Commitments' framework emphasizing clarity, inspiration, thought leadership, and results | Offers employees professional certification opportunities and tuition reimbursement for eligible staff</t>
+          <t>as a former standalone IT services firm (acquired by Atos in 2018 and later dissolved into Atos/Eviden), Syntel likely ran standard technology-services training such as onboarding bootcamps and vendor-certification tracks typical of its IT outsourcing peers | training programs were folded into Atos/Eviden's broader learning infrastructure post-acquisition rather than continuing under the Syntel brand | no current standalone L&amp;D reporting exists since Syntel is no longer an independent, reporting entity</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Insight Enterprises 10-K filings</t>
+          <t>No current public training data â€” entity absorbed into Atos/Eviden after 2018 acquisition</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ISG (Information Services Group)</t>
+          <t>Tata Consultancy Services (TCS) North America</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2066,31 +2076,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>https://www.isg-one.com</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1371489/000110465926024573/iii-20251231x10k.htm</t>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.tcs.com</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ISG Academy is the firm's global learning and development program covering industry/functional topics, leadership, certifications, and technical skills | In 2020, employees completed nearly 20,000 courses and logged 55,000+ learning hours; in 2021, 16,800+ courses and 31,000+ hours | Learning is bundled under the broader 'ISG WorkLife' set of Next-Gen HR programs aimed at talent attraction and retention</t>
+          <t>TCS employees logged 56 million learning hours and acquired 5.2 million competencies in FY25 (workforce ~608,000) | Average learning hours per employee rose over 25% to 120 hours in FY26, up from 96 hours in FY25 | AI-skilling was a major driver, with TCS reporting a 3x increase in AI skills training year-over-year</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ISG (Information Services Group) 10-K disclosures and ISG WorkLife program materials</t>
+          <t>TCS Integrated Annual Report 2025-26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JLL (Jones Lang LaSalle Incorporated)</t>
+          <t>Tech Mahindra Americas Inc.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2098,31 +2103,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>https://www.us.jll.com</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1037976/000103797626000037/jll-20251231.htm</t>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.techmahindra.com</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>More than 45,000 JLL employees completed a combined 127,000 dedicated sustainability learning courses in 2022/2023 | Formed a dedicated Sustainability Learning &amp; Development team in July 2022 to build sustainability skills across its ~100,000-person workforce, supporting its 2030 net-zero goal | Maintains a library of over 4,000 learning modules spanning live and e-learning formats company-wide</t>
+          <t>Tech Mahindra runs 'Upskilling-as-a-Service' (UaaS), an in-house AI-powered platform delivering personalized learning based on each employee's skills, role, and career goals | Company frames continuous learning as embedded workplace DNA to build a 'Fit for Future' workforce | Development approach is described as ongoing, personalized, and integrated into the day-to-day work experience</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JLL 10-K / Training APEX Award coverage</t>
+          <t>Tech Mahindra Integrated Annual Report FY2024-25</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KPMG LLP</t>
+          <t>The Hackett Group, Inc.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2130,26 +2130,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>https://www.kpmg.com</t>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.thehackettgroup.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1057379/000119312526082863/hckt-20251226.htm</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KPMG Lakehouse campus in Lake Nona, FL delivers over 1 million hours of in-person professional development annually for U.S. employees and partners | Advisory professionals are required to complete a minimum of 25 hours of learning each year | Offers a 'Learning as a Service' (LaaS) capability and extensive digital learning platforms covering leadership, data, and AI-era skills</t>
+          <t>The Hackett Group delivers ongoing associate training via webinars, on-the-job learning, and one-on-one coaching, plus a dedicated online learning technology platform | Education programs target key practice areas: business strategy, smart automation, cost optimization, global business services, and project management | Maintains technology/development labs so implementation specialists stay current on latest Oracle/SAP/OneStream software releases</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KPMG.com Learning &amp; Development Services pages</t>
+          <t>The Hackett Group FY2025 10-K (SEC)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Leidos Holdings, Inc.</t>
+          <t>ZS Associates, Inc.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2157,31 +2162,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>https://www.leidos.com</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1336920/000133692026000030/ldos-20260102.htm</t>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.zs.com</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Offers formal certification-prep programs for the Project Management Institute (PMI/PMP) and International Council on Systems Engineering, plus resources for 95+ other industry-standard professional/technical certifications | Provides tuition assistance to all U.S. full-time employees at accredited universities | Runs the 'Leidos Leadership' program along with targeted development for managers and executive leaders</t>
+          <t>ZS Associates runs a structured 'New to ZS' onboarding (two-week orientation) plus a milestones program for employees moving into new roles, supported by ZS University and leadership courses | Won Gold at the 2025 HCM Excellence Awards for Best Leadership Development Program and Best Unique/Innovative L&amp;D Program | Education sponsorship program offers structured tuition reimbursement to high performers with 30+ months of tenure</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leidos Holdings 10-K (FY2026)</t>
+          <t>ZS careers site and Built In company profile</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LTI (Larsen &amp; Toubro Infotech)</t>
+          <t>Kforce Inc.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2189,26 +2189,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>https://www.lntinfotech.com</t>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.kforce.com/</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/930420/000093042026000007/kfrc-20251231.htm</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Runs 'Learn Grow Lead' and Manager Development programs to build a pipeline of future-ready leaders, supplemented by AI-personalized career and learning pathways | Historically (FY2020-21 as LTI) delivered 2,500+ learning programs including 344+ competency-based behavioral/leadership and job-family learning tracks | Reports learning and development metrics annually in the 'Social' section of the LTIMindtree Integrated Annual Report</t>
+          <t>Kforce provides structured onboarding, training, mentorship, and continuous development programs for both internal staff and deployed consultants | Offers defined internal career-path options at hire to support long-term growth | Tracks consultant experience via NPS surveys, with 2025 results exceeding industry averages and achieving 'world-class' designation</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LTIMindtree Integrated Annual Report (2024-25)</t>
+          <t>Kforce Inc. FY2025 10-K (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ManpowerGroup Inc.</t>
+          <t>ASGN Incorporated</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2216,31 +2221,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>https://www.manpowergroup.com</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/871763/000119312526064113/man-20251231.htm</t>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.asgn.com/</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=ASGN</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ManpowerGroup's MyPath program has scaled to more than 301,000 associates for career pathways and upskilling into growth roles | Experis Academy has trained more than 4,500 developers and bridged skills gaps for 170+ tech companies across ~20 countries through 2025 | Future Leaders Program has graduated 1,166 employees since 2019, with 121 enrolled in 2025</t>
+          <t>ASGN treats career development and advancement as a top organizational priority, backed by ongoing education, professional development, and formal training | Runs a mentorship program pairing experienced professionals with mentees for career-development support | Training curriculum covers ethics/integrity, DEI, unconscious bias, cybersecurity/privacy, and workplace safety</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ManpowerGroup FY2025 10-K (SEC) and 2024-2025 Sustainability Report</t>
+          <t>ASGN Incorporated 10-K (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NTT DATA Services</t>
+          <t>Heidrick &amp; Struggles</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2248,26 +2253,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>https://www.nttdataservices.com</t>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.heidrick.com/</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=HSII</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>NTT DATA is training its ~200,000 global employees in foundational generative AI skills, with a goal of 30,000+ certified higher-level GenAI practitioners by FY2026 | Delivers training via its GenAI Academy, a multi-tiered self-paced learning, hands-on-lab program | Offers structured, tailored career-progression development paths from entry-level through management/leadership roles</t>
+          <t>Heidrick &amp; Struggles' Learning &amp; Development team delivered 10,500+ hours of facilitated training globally in 2023, with employees completing 5,000+ self-paced courses | Runs the Brandon Hall Award-winning Heidrick Business Academy for next-generation leader development | 'Heidrick Pathways' platform supports internal career mobility and mid-year/year-end talent reviews tied to succession planning</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NTT DATA Group press releases and corporate sustainability/HR pages</t>
+          <t>Heidrick &amp; Struggles International 10-K and GRI Index disclosures</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Protiviti Inc.</t>
+          <t>Korn Ferry</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2275,26 +2285,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>https://www.protiviti.com</t>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.kornferry.com/</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/56679/000005667926000021/kfy-20260430.htm</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Protiviti pays for employees to attain select recognized professional certifications as part of its benefits | Every Protiviti employee is assigned a career adviser who coaches them and recommends development actions | Annual operating plans include dedicated learning-budget funding plus milestone-based learning events at key career stages</t>
+          <t>Korn Ferry Academy draws on frameworks and insights from work with 15,000+ organizations worldwide to deliver leadership and talent-management training | Offers a five-module in-person program building strategic, analytical, and leadership capabilities for end-to-end talent management | Provides personalized, scaled learning journeys for sellers/project managers plus digital/sales leadership certification tracks</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Robert Half International 10-K human capital section and Protiviti careers pages</t>
+          <t>Korn Ferry FY2026 10-K (SEC) and Korn Ferry Academy program pages</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PwC (PricewaterhouseCoopers LLP)</t>
+          <t>Robert Half International Inc.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2302,26 +2317,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>https://www.pwc.com</t>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/315213/000031521326000006/rhi-20251231.htm</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PwC's average training hours per employee were 49.9 in FY23 (51.7 hrs for men, 47.9 for women), funded via ~Â£2,273 learning &amp; development spend per FTE | 93,000 PwC people have completed ESG training through its Global ESG Academy; 50,450 completed 'Inclusive Mindset' training | 39% of staff took learning courses outside their core area of expertise, part of a formal 'time away from role to learn' policy</t>
+          <t>Robert Half's enterprise values underpin its retention and development approach, cited in its 10-K human capital disclosures | Company employed ~14,500 full-time internal staff (incl. ~7,100 in Protiviti) as of year-end 2025, with career-development programs supporting its stated inclusion goals | Publishes management-focused L&amp;D guidance content as part of its broader talent-advisory positioning</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PwC Global Annual Review 2023-2025 and PwC Saratoga Workforce Index</t>
+          <t>Robert Half International FY2025 10-K (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RGP (Resources Global Professionals)</t>
+          <t>TrueBlue, Inc.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2329,26 +2349,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>https://www.rgp.com</t>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.trueblue.com/</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/768899/000076889926000009/tbi-20251228.htm</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Resources Connection (parent of RGP) 10-K human capital section emphasizes leadership development programs and mentorship as part of retention strategy | Culture and career-development investment centers on hybrid work, wellness, and employee wellbeing initiatives | Company frames talent development as a core differentiator in its flexible/on-demand consulting workforce model</t>
+          <t>TrueBlue positions itself as 'The People Company,' citing human capital management as central to its strategy in SEC filings | Invests in talent-management and development programs targeted at critical roles, alongside remote/hybrid work options | Employed approximately 3,500 full-time equivalent employees as of December 2025, a scale reflected in its people-development initiatives</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Resources Connection Inc. FY2025 10-K (SEC EDGAR)</t>
+          <t>TrueBlue Inc. FY2025 10-K (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Vaco, LLC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2356,26 +2381,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>https://www.slalom.com</t>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.vaco.com/</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Slalom (13,000+ team members) provides a free internal online learning library plus funding for third-party trainings and certifications | Runs a 'Road to Readiness' program guiding specific roles toward relevant AWS certifications | Offers multi-session, cohort-based offsite leadership-development programs for anyone in a people- or practice-management role</t>
+          <t>Vaco (10,000+ professionals across 45+ offices) maintains a dedicated Learning &amp; Development leadership function overseeing performance-management tools and learning-strategy design | Employee resource groups (ERGs) play an active role in shaping a continuous-learning, inclusive culture | Company markets professional growth and cross-industry project exposure as core career-development value propositions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Slalom careers site and AWS Training &amp; Certification blog</t>
+          <t>Vaco careers site and job postings for L&amp;D leadership roles</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Syntel Inc.</t>
+          <t>Aerotek, Inc.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2383,26 +2408,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>https://www.syntelinc.com</t>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.aerotek.com/</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>as a former standalone IT services firm (acquired by Atos in 2018 and later dissolved into Atos/Eviden), Syntel likely ran standard technology-services training such as onboarding bootcamps and vendor-certification tracks typical of its IT outsourcing peers | training programs were folded into Atos/Eviden's broader learning infrastructure post-acquisition rather than continuing under the Syntel brand | no current standalone L&amp;D reporting exists since Syntel is no longer an independent, reporting entity</t>
+          <t>Aerotek Academy offers three structured learning paths: a Role Academy for onboarding/upskilling, a Leadership Academy, and additional interpersonal-skills content | Parent Allegis Group evaluates leaders partly on how many people they have promoted and developed, embedding development into management accountability | Support extends beyond training to career counseling, financial education, and wellness initiatives for internal staff</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>No current public training data â€” entity absorbed into Atos/Eviden after 2018 acquisition</t>
+          <t>Aerotek company site and Allegis Group culture/press pages</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS) North America</t>
+          <t>Michael Page International</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2410,26 +2435,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>https://www.tcs.com</t>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com/</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TCS employees logged 56 million learning hours and acquired 5.2 million competencies in FY25 (workforce ~608,000) | Average learning hours per employee rose over 25% to 120 hours in FY26, up from 96 hours in FY25 | AI-skilling was a major driver, with TCS reporting a 3x increase in AI skills training year-over-year</t>
+          <t>PageGroup/Michael Page uses a market-leading blended learning approach combining video, e-learning, gamification, and virtual/physical classroom sessions | New joiners follow a structured global onboarding programme plus a formal training path delivered by operational managers and directors | Senior leaders receive external executive coaching tied to the 'PageGroup Potential' leadership development model</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>TCS Integrated Annual Report 2025-26</t>
+          <t>PageGroup/Michael Page careers pages, annual report references</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Tech Mahindra Americas Inc.</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2437,26 +2462,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>https://www.techmahindra.com</t>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.epam.com/</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1352010/000135201026000015/epam-20251231.htm</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Tech Mahindra runs 'Upskilling-as-a-Service' (UaaS), an in-house AI-powered platform delivering personalized learning based on each employee's skills, role, and career goals | Company frames continuous learning as embedded workplace DNA to build a 'Fit for Future' workforce | Development approach is described as ongoing, personalized, and integrated into the day-to-day work experience</t>
+          <t>FY2025 10-K reports approximately 62,850 employees, ~56,600 delivery professionals, with human capital strategy centered on ongoing skills development and continuous rotation/promotion opportunities | Company states success depends on hiring, training, developing and deploying talent to meet client demand, with explicit focus on cultivating next-generation leaders and succession pipelines | Invests in employee wellness/well-being programs alongside professional development as part of its talent retention strategy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tech Mahindra Integrated Annual Report FY2024-25</t>
+          <t>EPAM Systems FY2025 Form 10-K (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>The Hackett Group, Inc.</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2464,31 +2494,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>https://www.thehackettgroup.com</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1057379/000119312526082863/hckt-20251226.htm</t>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.luxoft.com/</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>The Hackett Group delivers ongoing associate training via webinars, on-the-job learning, and one-on-one coaching, plus a dedicated online learning technology platform | Education programs target key practice areas: business strategy, smart automation, cost optimization, global business services, and project management | Maintains technology/development labs so implementation specialists stay current on latest Oracle/SAP/OneStream software releases</t>
+          <t>as a legacy Luxoft entity now absorbed into DXC Technology since the 2019 acquisition, standalone training data is no longer reported separately | legacy Luxoft software-engineering training tracks (technical certifications, engineering academies) were folded into DXC's broader L&amp;D infrastructure | current employees formerly under the Luxoft brand now follow DXC Technology's global learning management ecosystem</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>The Hackett Group FY2025 10-K (SEC)</t>
+          <t>General knowledge of post-acquisition corporate reporting practices (Luxoft acquired by DXC in 2019)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Wipro Limited</t>
+          <t>Mindtree</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2496,31 +2521,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>https://www.wipro.com</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=WIT</t>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.mindtree.com/</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Wipro trained over 225,000 employees in generative AI skills (as of FY2023-24) | 85% of employees completed the company's mandatory annual Code of Business Conduct training in FY2025-26 | Runs a Work Integrated Learning Program (earn-and-learn model) alongside its broader Integrated Annual/Sustainability Report learning disclosures</t>
+          <t>Employee development anchored by the 'My Career My Growth' framework plus 'Learn Grow Lead' and Manager Development programs building future-ready leadership pipelines | Manager Development Program for first-time managers includes e-learning modules, workshops, and unconscious-bias training | 'Campus Full Potential' university-liaison program integrates industry-ready skilling with academic curricula, bringing in roughly 9,000-10,000 fresh graduate hires annually</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wipro Integrated Annual Report FY2025-26</t>
+          <t>LTIMindtree Integrated Annual Report 2024-25</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ZS Associates, Inc.</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2528,26 +2548,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>https://www.zs.com</t>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.mphasis.com/</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ZS Associates runs a structured 'New to ZS' onboarding (two-week orientation) plus a milestones program for employees moving into new roles, supported by ZS University and leadership courses | Won Gold at the 2025 HCM Excellence Awards for Best Leadership Development Program and Best Unique/Innovative L&amp;D Program | Education sponsorship program offers structured tuition reimbursement to high performers with 30+ months of tenure</t>
+          <t>Talent Next is Mphasis's proprietary learning platform, evolved into a full HR ecosystem offering over 750 skill areas via instructor-led training, eLearning, cloud labs, and gamified/social learning | In FY23 Mphasis expanded learning content in next-gen digital skills including AI/ML, Cloud, DevOps, Big Data, and Cybersecurity | Learning resources include assessments and certifications integrated directly into the Talent Next platform for continuous skill tracking</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ZS careers site and Built In company profile</t>
+          <t>Mphasis Annual Report / careers.mphasis.com</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kforce Inc.</t>
+          <t>NTT DATA, Inc.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2555,31 +2575,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>https://www.kforce.com/</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/930420/000093042026000007/kfrc-20251231.htm</t>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.nttdata.com/</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kforce provides structured onboarding, training, mentorship, and continuous development programs for both internal staff and deployed consultants | Offers defined internal career-path options at hire to support long-term growth | Tracks consultant experience via NPS surveys, with 2025 results exceeding industry averages and achieving 'world-class' designation</t>
+          <t>GenAI Academy delivers unified, multi-tiered AI literacy and skills training across NTT DATA's workforce in 70+ countries, and won a Brandon Hall Group Learning &amp; Development Gold Award | Career development includes NTT University and an Executive Academy offering dialogues with current executives | Structured, stage-specific development programs support career progression, including global business role assignments and external management seminars</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kforce Inc. FY2025 10-K (SEC EDGAR)</t>
+          <t>NTT DATA Group sustainability/human resource pages</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ASGN Incorporated</t>
+          <t>Perficient, Inc.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2587,31 +2602,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>https://www.asgn.com/</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=ASGN</t>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.perficient.com/</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=PRFT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ASGN treats career development and advancement as a top organizational priority, backed by ongoing education, professional development, and formal training | Runs a mentorship program pairing experienced professionals with mentees for career-development support | Training curriculum covers ethics/integrity, DEI, unconscious bias, cybersecurity/privacy, and workplace safety</t>
+          <t>Historic 10-K filings describe an IBM-certified advanced training facility in Chicago used for continuing education and professional development of technology staff | Professionals receive training in implementation methodology and project management critical to consulting engagements, plus individualized professional development plans tied to annual reviews | Company reports two-year voluntary attrition around 15%, which it attributes partly to its career development and training investment</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ASGN Incorporated 10-K (SEC EDGAR)</t>
+          <t>Perficient Inc. Form 10-K filings (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Heidrick &amp; Struggles</t>
+          <t>Pegasystems Inc.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2619,31 +2634,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>https://www.heidrick.com/</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=HSII</t>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.pega.com/</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1013857/000101385726000017/pega-20251231.htm</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Heidrick &amp; Struggles' Learning &amp; Development team delivered 10,500+ hours of facilitated training globally in 2023, with employees completing 5,000+ self-paced courses | Runs the Brandon Hall Award-winning Heidrick Business Academy for next-generation leader development | 'Heidrick Pathways' platform supports internal career mobility and mid-year/year-end talent reviews tied to succession planning</t>
+          <t>FY2025 10-K describes lifelong learning and curiosity as core company values, with growth supported through mentorship, job shadowing, on-demand learning, and structured development programs | Pega Academy is the company's dedicated platform accelerating skill development for employees, clients, and partners on emerging technologies | Leadership development programs are paired with education reimbursement and external partnerships; workforce reported at 5,598 employees as of January 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Heidrick &amp; Struggles International 10-K and GRI Index disclosures</t>
+          <t>Pegasystems Inc. FY2025 Form 10-K (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Korn Ferry</t>
+          <t>SAP America, Inc.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2651,31 +2666,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>https://www.kornferry.com/</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/56679/000005667926000021/kfy-20260430.htm</t>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Korn Ferry Academy draws on frameworks and insights from work with 15,000+ organizations worldwide to deliver leadership and talent-management training | Offers a five-module in-person program building strategic, analytical, and leadership capabilities for end-to-end talent management | Provides personalized, scaled learning journeys for sellers/project managers plus digital/sales leadership certification tracks</t>
+          <t>SAP SuccessFactors Learning and the Integrated Learning Experience power internal upskilling as well as SAP's commercial LMS offering, reflecting a stated corporate learning culture | SAP publishes learning/training metrics in its annual SAP Integrated Report as part of ESG-aligned human capital disclosures | SAP Learning Hub provides e-learning and formal certification tracks used both internally and for customer/partner enablement</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korn Ferry FY2026 10-K (SEC) and Korn Ferry Academy program pages</t>
+          <t>SAP Integrated Report 2025, SAP Insights learning culture pages</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Robert Half International Inc.</t>
+          <t>Sierra-Cedar, Inc.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2683,31 +2693,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>https://www.roberthalf.com/</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/315213/000031521326000006/rhi-20251231.htm</t>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.sierracedar.com/</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Robert Half's enterprise values underpin its retention and development approach, cited in its 10-K human capital disclosures | Company employed ~14,500 full-time internal staff (incl. ~7,100 in Protiviti) as of year-end 2025, with career-development programs supporting its stated inclusion goals | Publishes management-focused L&amp;D guidance content as part of its broader talent-advisory positioning</t>
+          <t>as a legacy Sierra-Cedar entity absorbed into Mercer/Marsh McLennan since the 2021 acquisition, standalone L&amp;D reporting is no longer published separately | any remaining training programs would now be folded into Mercer's broader consulting workforce development framework | certification support (e.g., ERP/HR systems credentials) would continue informally but without independent public disclosure</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Robert Half International FY2025 10-K (SEC EDGAR)</t>
+          <t>General knowledge of post-acquisition corporate reporting practices</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TrueBlue, Inc.</t>
+          <t>Sogeti USA LLC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2715,31 +2720,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>https://www.trueblue.com/</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/768899/000076889926000009/tbi-20251228.htm</t>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.sogeti.com/</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>TrueBlue positions itself as 'The People Company,' citing human capital management as central to its strategy in SEC filings | Invests in talent-management and development programs targeted at critical roles, alongside remote/hybrid work options | Employed approximately 3,500 full-time equivalent employees as of December 2025, a scale reflected in its people-development initiatives</t>
+          <t>Capgemini (Sogeti's parent group) targets a 5% annual increase in average learning hours per employee as a stated ESG objective | Capgemini Academy offers 300+ courses across Tech, Methods &amp; Certifications, and Leadership domains, used group-wide including by Sogeti staff | Sogeti runs its own leadership development track called SoLEAD, aimed at nurturing the next generation of Sogeti leaders</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>TrueBlue Inc. FY2025 10-K (SEC EDGAR)</t>
+          <t>Capgemini Integrated Annual Report / Capgemini Academy pages</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Vaco, LLC</t>
+          <t>Sopra Steria, Inc.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2747,26 +2747,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>https://www.vaco.com/</t>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.us/</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vaco (10,000+ professionals across 45+ offices) maintains a dedicated Learning &amp; Development leadership function overseeing performance-management tools and learning-strategy design | Employee resource groups (ERGs) play an active role in shaping a continuous-learning, inclusive culture | Company markets professional growth and cross-industry project exposure as core career-development value propositions</t>
+          <t>Training catalog includes Group fundamentals/management courses, new-employee induction, business-specific and technology courses (cloud, agility, end-to-end delivery) | Redesigned onboarding program 'Immediate Boarding' delivered training to over 1,500 new recruits via face-to-face and remote sessions | 'New Skill' pathways combine formal training with role-immersion periods; online training platform adoption increased total digital training delivery by 20%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vaco careers site and job postings for L&amp;D leadership roles</t>
+          <t>Sopra Steria Universal Registration Document</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Aerotek, Inc.</t>
+          <t>TechTarget</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2774,26 +2774,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>https://www.aerotek.com/</t>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.techtarget.com/</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2018064/000119312526102183/ttgt-20251231.htm</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aerotek Academy offers three structured learning paths: a Role Academy for onboarding/upskilling, a Leadership Academy, and additional interpersonal-skills content | Parent Allegis Group evaluates leaders partly on how many people they have promoted and developed, embedding development into management accountability | Support extends beyond training to career counseling, financial education, and wellness initiatives for internal staff</t>
+          <t>as a mid-size B2B media/data company, TechTarget likely maintains standard professional development budgets and manager-led training rather than large named corporate academies | its FY2025 10-K human capital section would reference employee training and development in generic terms consistent with similar-sized public media/tech companies | no large-scale certification partnership (e.g., PMI) would be publicly highlighted given its media/research business model</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aerotek company site and Allegis Group culture/press pages</t>
+          <t>TechTarget FY2025 10-K not directly retrievable via search</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Michael Page International</t>
+          <t>UST Global</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2801,26 +2806,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.com/</t>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.ust-global.com/</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PageGroup/Michael Page uses a market-leading blended learning approach combining video, e-learning, gamification, and virtual/physical classroom sessions | New joiners follow a structured global onboarding programme plus a formal training path delivered by operational managers and directors | Senior leaders receive external executive coaching tied to the 'PageGroup Potential' leadership development model</t>
+          <t>'Born to Learn' is described as a foundational UST cultural pillar emphasizing learning agility as employees' most critical core competency | UST Step It Up is an apprenticeship program recruiting and training new technical talent for digital transformation roles | Reported program results: about 1,500 employees participated in L&amp;D initiatives completing 3,500+ courses, with the broader workforce logging nearly 10,000 learning hours every four months and 15% reskilled into new business lines</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PageGroup/Michael Page careers pages, annual report references</t>
+          <t>UST careers/Step It Up pages, Udemy Business and Pluralsight case studies on UST</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Virtusa Corporation</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2828,31 +2833,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>https://www.epam.com/</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1352010/000135201026000015/epam-20251231.htm</t>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.virtusa.com/</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FY2025 10-K reports approximately 62,850 employees, ~56,600 delivery professionals, with human capital strategy centered on ongoing skills development and continuous rotation/promotion opportunities | Company states success depends on hiring, training, developing and deploying talent to meet client demand, with explicit focus on cultivating next-generation leaders and succession pipelines | Invests in employee wellness/well-being programs alongside professional development as part of its talent retention strategy</t>
+          <t>Offers a Digital Training Solutions practice delivering personalized, blended training programs, though primarily a client-facing service line rather than solely internal | Internal fresher training is decentralized, delivered depending on each new hire's joining location rather than through one central academy | as a company taken private by Baring Private Equity Asia in 2021, detailed internal L&amp;D metrics are no longer publicly disclosed</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>EPAM Systems FY2025 Form 10-K (SEC EDGAR)</t>
+          <t>Virtusa Digital Training Solutions and careers pages</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>West Monroe Partners</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2860,26 +2860,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>https://www.luxoft.com/</t>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.westmonroepartners.com/</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>as a legacy Luxoft entity now absorbed into DXC Technology since the 2019 acquisition, standalone training data is no longer reported separately | legacy Luxoft software-engineering training tracks (technical certifications, engineering academies) were folded into DXC's broader L&amp;D infrastructure | current employees formerly under the Luxoft brand now follow DXC Technology's global learning management ecosystem</t>
+          <t>West Monroe University offers hundreds of internal courses covering technical skills and leadership development for all consulting staff | Firm provides dedicated learning budgets for full-time employees to pursue external professional certifications | Culture emphasizes mentorship-driven development alongside a target 50-55 hour average workweek framed as 'sustainable high performance'</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>General knowledge of post-acquisition corporate reporting practices (Luxoft acquired by DXC in 2019)</t>
+          <t>West Monroe careers/professional development pages</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Mindtree</t>
+          <t>Zensar Technologies, Inc.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2887,26 +2887,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>https://www.mindtree.com/</t>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.zensar.com/</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Employee development anchored by the 'My Career My Growth' framework plus 'Learn Grow Lead' and Manager Development programs building future-ready leadership pipelines | Manager Development Program for first-time managers includes e-learning modules, workshops, and unconscious-bias training | 'Campus Full Potential' university-liaison program integrates industry-ready skilling with academic curricula, bringing in roughly 9,000-10,000 fresh graduate hires annually</t>
+          <t>Ignite AI Academy drove AI upskilling across 85% of Zensar's workforce, with AI learning hours per person up 136% in FY26 | Development Action Plan (DAP) competency program reached 9,000+ employees, with 84% completion in FY24 | Zenlear, Zensar's AI-enabled learning platform, tracks each employee's functional, behavioral, and technical competency development via web portal and mobile app</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>LTIMindtree Integrated Annual Report 2024-25</t>
+          <t>Zensar Technologies careers/Learning Academy page, Q4 FY26 earnings call transcript</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Collabera Inc.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2914,26 +2914,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>https://www.mphasis.com/</t>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.collabera.com/</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Talent Next is Mphasis's proprietary learning platform, evolved into a full HR ecosystem offering over 750 skill areas via instructor-led training, eLearning, cloud labs, and gamified/social learning | In FY23 Mphasis expanded learning content in next-gen digital skills including AI/ML, Cloud, DevOps, Big Data, and Cybersecurity | Learning resources include assessments and certifications integrated directly into the Talent Next platform for continuous skill tracking</t>
+          <t>Talent Development and Transformation practice covers upskilling/reskilling curricula in cloud computing, cybersecurity, and machine learning, offered with 24/7 digital resource access and mentorship | Hire, Train and Deploy (HTD) Managed Capacity service builds long-term talent pipelines through structured training before client deployment | Account Management Program gives new graduates and entry-level hires structured mentorship with a defined Associate-to-Account-Manager career trajectory</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mphasis Annual Report / careers.mphasis.com</t>
+          <t>Collabera Talent Development and Transformation, careers pages</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NTT DATA, Inc.</t>
+          <t>iGATE Corporation</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2941,26 +2941,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>https://www.nttdata.com/</t>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.igate.com/</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>GenAI Academy delivers unified, multi-tiered AI literacy and skills training across NTT DATA's workforce in 70+ countries, and won a Brandon Hall Group Learning &amp; Development Gold Award | Career development includes NTT University and an Executive Academy offering dialogues with current executives | Structured, stage-specific development programs support career progression, including global business role assignments and external management seminars</t>
+          <t>as an entity absorbed into Capgemini following the 2015 acquisition, iGATE no longer maintains standalone training programs or public L&amp;D disclosures | any legacy iGATE training infrastructure (e.g., its former iLearn platform) would now be integrated into Capgemini's broader Academy and Talent Learning Academy systems | certification support formerly offered under the iGATE brand would now fall under Capgemini's group-wide learning policies</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NTT DATA Group sustainability/human resource pages</t>
+          <t>General knowledge of post-acquisition corporate reporting practices</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Perficient, Inc.</t>
+          <t>Hexaware Technologies, Inc.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2968,529 +2968,23 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>https://www.perficient.com/</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=PRFT</t>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.hexaware.com/</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Historic 10-K filings describe an IBM-certified advanced training facility in Chicago used for continuing education and professional development of technology staff | Professionals receive training in implementation methodology and project management critical to consulting engagements, plus individualized professional development plans tied to annual reviews | Company reports two-year voluntary attrition around 15%, which it attributes partly to its career development and training investment</t>
+          <t>HexaVarsity is Hexaware's overarching L&amp;D framework; its SONIC program gives employees access to 1,000+ external certifications, 350+ curated learning paths, hackathons, and unlimited certification reimbursement | Mavericks (graduate program) and HFLX (fast-track management trainee program) provide structured onboarding, rotations, and accelerated leadership exposure for early-career hires | Reported impact: 44,000+ advanced certifications achieved, 81% of the tech workforce trained digitally, and 3% lower attrition among HexaVarsity participants</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Perficient Inc. Form 10-K filings (SEC EDGAR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Pegasystems Inc.</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>https://www.pega.com/</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1013857/000101385726000017/pega-20251231.htm</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>FY2025 10-K describes lifelong learning and curiosity as core company values, with growth supported through mentorship, job shadowing, on-demand learning, and structured development programs | Pega Academy is the company's dedicated platform accelerating skill development for employees, clients, and partners on emerging technologies | Leadership development programs are paired with education reimbursement and external partnerships; workforce reported at 5,598 employees as of January 2026</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Pegasystems Inc. FY2025 Form 10-K (SEC EDGAR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>SAP America, Inc.</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sap.com/</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>SAP SuccessFactors Learning and the Integrated Learning Experience power internal upskilling as well as SAP's commercial LMS offering, reflecting a stated corporate learning culture | SAP publishes learning/training metrics in its annual SAP Integrated Report as part of ESG-aligned human capital disclosures | SAP Learning Hub provides e-learning and formal certification tracks used both internally and for customer/partner enablement</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>SAP Integrated Report 2025, SAP Insights learning culture pages</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Sierra-Cedar, Inc.</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sierracedar.com/</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>as a legacy Sierra-Cedar entity absorbed into Mercer/Marsh McLennan since the 2021 acquisition, standalone L&amp;D reporting is no longer published separately | any remaining training programs would now be folded into Mercer's broader consulting workforce development framework | certification support (e.g., ERP/HR systems credentials) would continue informally but without independent public disclosure</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>General knowledge of post-acquisition corporate reporting practices</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sogeti USA LLC</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sogeti.com/</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Capgemini (Sogeti's parent group) targets a 5% annual increase in average learning hours per employee as a stated ESG objective | Capgemini Academy offers 300+ courses across Tech, Methods &amp; Certifications, and Leadership domains, used group-wide including by Sogeti staff | Sogeti runs its own leadership development track called SoLEAD, aimed at nurturing the next generation of Sogeti leaders</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Capgemini Integrated Annual Report / Capgemini Academy pages</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Sopra Steria, Inc.</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>https://www.soprasteria.us/</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Training catalog includes Group fundamentals/management courses, new-employee induction, business-specific and technology courses (cloud, agility, end-to-end delivery) | Redesigned onboarding program 'Immediate Boarding' delivered training to over 1,500 new recruits via face-to-face and remote sessions | 'New Skill' pathways combine formal training with role-immersion periods; online training platform adoption increased total digital training delivery by 20%</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Sopra Steria Universal Registration Document</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>TechTarget</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>https://www.techtarget.com/</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2018064/000119312526102183/ttgt-20251231.htm</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>as a mid-size B2B media/data company, TechTarget likely maintains standard professional development budgets and manager-led training rather than large named corporate academies | its FY2025 10-K human capital section would reference employee training and development in generic terms consistent with similar-sized public media/tech companies | no large-scale certification partnership (e.g., PMI) would be publicly highlighted given its media/research business model</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>TechTarget FY2025 10-K not directly retrievable via search</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>UST Global</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>https://www.ust-global.com/</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>'Born to Learn' is described as a foundational UST cultural pillar emphasizing learning agility as employees' most critical core competency | UST Step It Up is an apprenticeship program recruiting and training new technical talent for digital transformation roles | Reported program results: about 1,500 employees participated in L&amp;D initiatives completing 3,500+ courses, with the broader workforce logging nearly 10,000 learning hours every four months and 15% reskilled into new business lines</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>UST careers/Step It Up pages, Udemy Business and Pluralsight case studies on UST</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Virtusa Corporation</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>https://www.virtusa.com/</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Offers a Digital Training Solutions practice delivering personalized, blended training programs, though primarily a client-facing service line rather than solely internal | Internal fresher training is decentralized, delivered depending on each new hire's joining location rather than through one central academy | as a company taken private by Baring Private Equity Asia in 2021, detailed internal L&amp;D metrics are no longer publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Virtusa Digital Training Solutions and careers pages</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>West Monroe Partners</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>https://www.westmonroepartners.com/</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>West Monroe University offers hundreds of internal courses covering technical skills and leadership development for all consulting staff | Firm provides dedicated learning budgets for full-time employees to pursue external professional certifications | Culture emphasizes mentorship-driven development alongside a target 50-55 hour average workweek framed as 'sustainable high performance'</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>West Monroe careers/professional development pages</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Zensar Technologies, Inc.</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C98" s="1" t="inlineStr">
-        <is>
-          <t>https://www.zensar.com/</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Ignite AI Academy drove AI upskilling across 85% of Zensar's workforce, with AI learning hours per person up 136% in FY26 | Development Action Plan (DAP) competency program reached 9,000+ employees, with 84% completion in FY24 | Zenlear, Zensar's AI-enabled learning platform, tracks each employee's functional, behavioral, and technical competency development via web portal and mobile app</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Zensar Technologies careers/Learning Academy page, Q4 FY26 earnings call transcript</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Collabera Inc.</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>https://www.collabera.com/</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Talent Development and Transformation practice covers upskilling/reskilling curricula in cloud computing, cybersecurity, and machine learning, offered with 24/7 digital resource access and mentorship | Hire, Train and Deploy (HTD) Managed Capacity service builds long-term talent pipelines through structured training before client deployment | Account Management Program gives new graduates and entry-level hires structured mentorship with a defined Associate-to-Account-Manager career trajectory</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Collabera Talent Development and Transformation, careers pages</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>iGATE Corporation</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>https://www.igate.com/</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>as an entity absorbed into Capgemini following the 2015 acquisition, iGATE no longer maintains standalone training programs or public L&amp;D disclosures | any legacy iGATE training infrastructure (e.g., its former iLearn platform) would now be integrated into Capgemini's broader Academy and Talent Learning Academy systems | certification support formerly offered under the iGATE brand would now fall under Capgemini's group-wide learning policies</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>General knowledge of post-acquisition corporate reporting practices</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Hexaware Technologies, Inc.</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>https://www.hexaware.com/</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>HexaVarsity is Hexaware's overarching L&amp;D framework; its SONIC program gives employees access to 1,000+ external certifications, 350+ curated learning paths, hackathons, and unlimited certification reimbursement | Mavericks (graduate program) and HFLX (fast-track management trainee program) provide structured onboarding, rotations, and accelerated leadership exposure for early-career hires | Reported impact: 44,000+ advanced certifications achieved, 81% of the tech workforce trained digitally, and 3% lower attrition among HexaVarsity participants</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
           <t>Hexaware HexaVarsity learning and development pages, Hexaware Annual Report 2024/2025</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId138"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/research/PMP_ITES_Companies_USA.xlsx
+++ b/research/PMP_ITES_Companies_USA.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>publishes detailed training-hour and skilling metrics in its FY2025-26 Integrated Annual Report / Business Responsibility and Sustainability Report, following industry-standard IT-services disclosure practice | operates structured learning delivery via virtual instructor-led training, self-paced modules, and gamified learning journeys | ties learning investment to compliance and role-based training completion alongside technical/AI upskilling programs</t>
+          <t>Publishes detailed training-hour and skilling metrics in its FY2025-26 Integrated Annual Report / Business Responsibility and Sustainability Report, following industry-standard IT-services disclosure practice | Operates structured learning delivery via virtual instructor-led training, self-paced modules, and gamified learning journeys | Ties learning investment to compliance and role-based training completion alongside technical/AI upskilling programs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DHG (Dixon Hughes Goodman) merged into Forvis in June 2022 and no longer operates independently or publishes standalone training disclosures | prior to the merger, DHG offered typical mid-tier accounting-firm CPA exam support, mentoring and CPE programs consistent with industry norms | legacy DHG training programs were folded into Forvis Mazars' current learning and development framework post-merger</t>
+          <t>DHG (Dixon Hughes Goodman) merged into Forvis in June 2022 and no longer operates independently or publishes standalone training disclosures | Prior to the merger, DHG offered typical mid-tier accounting-firm CPA exam support, mentoring and CPE programs consistent with industry norms | Legacy DHG training programs were folded into Forvis Mazars' current learning and development framework post-merger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>as a BPO/call-center operator (acquired by Synnex/Concentrix in 2018 and now defunct as a standalone entity), Convergys would have run structured agent-training and quality-certification programs typical of the customer-care outsourcing industry | Historically acquired DigitalThink, a San Francisco e-learning provider, for $120 million in 2004 to build out workforce e-learning/training platforms for clients | Convergys Philippines was named 'BPO Employer of the Year' in 2012, reflecting recognized training/development practices across its 26,000-employee Philippine operation</t>
+          <t>As a BPO/call-center operator (acquired by Synnex/Concentrix in 2018 and now defunct as a standalone entity), Convergys would have run structured agent-training and quality-certification programs typical of the customer-care outsourcing industry | Historically acquired DigitalThink, a San Francisco e-learning provider, for $120 million in 2004 to build out workforce e-learning/training platforms for clients | Convergys Philippines was named 'BPO Employer of the Year' in 2012, reflecting recognized training/development practices across its 26,000-employee Philippine operation</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>as a former standalone IT services firm (acquired by Atos in 2018 and later dissolved into Atos/Eviden), Syntel likely ran standard technology-services training such as onboarding bootcamps and vendor-certification tracks typical of its IT outsourcing peers | training programs were folded into Atos/Eviden's broader learning infrastructure post-acquisition rather than continuing under the Syntel brand | no current standalone L&amp;D reporting exists since Syntel is no longer an independent, reporting entity</t>
+          <t>As a former standalone IT services firm (acquired by Atos in 2018 and later dissolved into Atos/Eviden), Syntel likely ran standard technology-services training such as onboarding bootcamps and vendor-certification tracks typical of its IT outsourcing peers | Training programs were folded into Atos/Eviden's broader learning infrastructure post-acquisition rather than continuing under the Syntel brand | No current standalone L&amp;D reporting exists since Syntel is no longer an independent, reporting entity</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>as a legacy Luxoft entity now absorbed into DXC Technology since the 2019 acquisition, standalone training data is no longer reported separately | legacy Luxoft software-engineering training tracks (technical certifications, engineering academies) were folded into DXC's broader L&amp;D infrastructure | current employees formerly under the Luxoft brand now follow DXC Technology's global learning management ecosystem</t>
+          <t>As a legacy Luxoft entity now absorbed into DXC Technology since the 2019 acquisition, standalone training data is no longer reported separately | Legacy Luxoft software-engineering training tracks (technical certifications, engineering academies) were folded into DXC's broader L&amp;D infrastructure | Current employees formerly under the Luxoft brand now follow DXC Technology's global learning management ecosystem</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>as a legacy Sierra-Cedar entity absorbed into Mercer/Marsh McLennan since the 2021 acquisition, standalone L&amp;D reporting is no longer published separately | any remaining training programs would now be folded into Mercer's broader consulting workforce development framework | certification support (e.g., ERP/HR systems credentials) would continue informally but without independent public disclosure</t>
+          <t>As a legacy Sierra-Cedar entity absorbed into Mercer/Marsh McLennan since the 2021 acquisition, standalone L&amp;D reporting is no longer published separately | Any remaining training programs would now be folded into Mercer's broader consulting workforce development framework | Certification support (e.g., ERP/HR systems credentials) would continue informally but without independent public disclosure</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>as a mid-size B2B media/data company, TechTarget likely maintains standard professional development budgets and manager-led training rather than large named corporate academies | its FY2025 10-K human capital section would reference employee training and development in generic terms consistent with similar-sized public media/tech companies | no large-scale certification partnership (e.g., PMI) would be publicly highlighted given its media/research business model</t>
+          <t>As a mid-size B2B media/data company, TechTarget likely maintains standard professional development budgets and manager-led training rather than large named corporate academies | Its FY2025 10-K human capital section would reference employee training and development in generic terms consistent with similar-sized public media/tech companies | No large-scale certification partnership (e.g., PMI) would be publicly highlighted given its media/research business model</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Offers a Digital Training Solutions practice delivering personalized, blended training programs, though primarily a client-facing service line rather than solely internal | Internal fresher training is decentralized, delivered depending on each new hire's joining location rather than through one central academy | as a company taken private by Baring Private Equity Asia in 2021, detailed internal L&amp;D metrics are no longer publicly disclosed</t>
+          <t>Offers a Digital Training Solutions practice delivering personalized, blended training programs, though primarily a client-facing service line rather than solely internal | Internal fresher training is decentralized, delivered depending on each new hire's joining location rather than through one central academy | As a company taken private by Baring Private Equity Asia in 2021, detailed internal L&amp;D metrics are no longer publicly disclosed</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>as an entity absorbed into Capgemini following the 2015 acquisition, iGATE no longer maintains standalone training programs or public L&amp;D disclosures | any legacy iGATE training infrastructure (e.g., its former iLearn platform) would now be integrated into Capgemini's broader Academy and Talent Learning Academy systems | certification support formerly offered under the iGATE brand would now fall under Capgemini's group-wide learning policies</t>
+          <t>As an entity absorbed into Capgemini following the 2015 acquisition, iGATE no longer maintains standalone training programs or public L&amp;D disclosures | Any legacy iGATE training infrastructure (e.g., its former iLearn platform) would now be integrated into Capgemini's broader Academy and Talent Learning Academy systems | Certification support formerly offered under the iGATE brand would now fall under Capgemini's group-wide learning policies</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
